--- a/reports/student_report.xlsx
+++ b/reports/student_report.xlsx
@@ -1,43 +1,236 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Student Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Student Ranking" sheetId="3" r:id="rId3"/>
+    <sheet name="Subject Performance Distributio" sheetId="4" r:id="rId4"/>
+    <sheet name="Student Performance Trend" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Student Data'!$A$1:$J$26</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="50">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>TeamWork</t>
+  </si>
+  <si>
+    <t>MidTerm</t>
+  </si>
+  <si>
+    <t>FinalExam</t>
+  </si>
+  <si>
+    <t>Scores</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Student 1</t>
+  </si>
+  <si>
+    <t>Student 2</t>
+  </si>
+  <si>
+    <t>Student 3</t>
+  </si>
+  <si>
+    <t>Student 4</t>
+  </si>
+  <si>
+    <t>Student 5</t>
+  </si>
+  <si>
+    <t>Student 6</t>
+  </si>
+  <si>
+    <t>Student 7</t>
+  </si>
+  <si>
+    <t>Student 8</t>
+  </si>
+  <si>
+    <t>Student 9</t>
+  </si>
+  <si>
+    <t>Student 10</t>
+  </si>
+  <si>
+    <t>Student 11</t>
+  </si>
+  <si>
+    <t>Student 12</t>
+  </si>
+  <si>
+    <t>Student 13</t>
+  </si>
+  <si>
+    <t>Student 14</t>
+  </si>
+  <si>
+    <t>Student 15</t>
+  </si>
+  <si>
+    <t>Student 16</t>
+  </si>
+  <si>
+    <t>Student 17</t>
+  </si>
+  <si>
+    <t>Student 18</t>
+  </si>
+  <si>
+    <t>Student 19</t>
+  </si>
+  <si>
+    <t>Student 20</t>
+  </si>
+  <si>
+    <t>Student 21</t>
+  </si>
+  <si>
+    <t>Student 22</t>
+  </si>
+  <si>
+    <t>Student 23</t>
+  </si>
+  <si>
+    <t>Student 24</t>
+  </si>
+  <si>
+    <t>Student 25</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Student Performance Summary Report</t>
+  </si>
+  <si>
+    <t>Generated: 2025-11-03</t>
+  </si>
+  <si>
+    <t>Key Statistics</t>
+  </si>
+  <si>
+    <t>Overall Average:</t>
+  </si>
+  <si>
+    <t>11.89</t>
+  </si>
+  <si>
+    <t>Pass Rate:</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>Total Students:</t>
+  </si>
+  <si>
+    <t>Student Ranking</t>
+  </si>
+  <si>
+    <t>Subject Performance Distribution</t>
+  </si>
+  <si>
+    <t>Student Performance Trend</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CAF50"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2196F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,95 +238,158 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Student_Ranking.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="381000"/>
+          <a:ext cx="9144000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Subject_Performance_Distribution.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="381000"/>
+          <a:ext cx="9144000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Student_Performance_Trend.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="381000"/>
+          <a:ext cx="9144000" cy="4572000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -420,135 +676,992 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Math</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Science</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Attendance</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Alice</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>2.5</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2.3</v>
+      </c>
+      <c r="G2">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2">
+        <v>4.716666666666667</v>
+      </c>
+      <c r="J2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>5.1</v>
+      </c>
+      <c r="C3">
+        <v>1.5</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>4.9</v>
+      </c>
+      <c r="G3">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3">
+        <v>10.5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>2.9</v>
+      </c>
+      <c r="G4">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4">
+        <v>6.266666666666667</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>8.5</v>
+      </c>
+      <c r="C5">
+        <v>3.7</v>
+      </c>
+      <c r="D5">
+        <v>1.2</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>7.7</v>
+      </c>
+      <c r="G5">
+        <v>75</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5">
+        <v>17.18333333333333</v>
+      </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>1.2</v>
+      </c>
+      <c r="D6">
+        <v>0.3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3.2</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6">
+        <v>6.866666666666667</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>1.5</v>
+      </c>
+      <c r="C7">
+        <v>0.2</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2.2</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7">
+        <v>4.316666666666666</v>
+      </c>
+      <c r="J7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="C8">
+        <v>4.8</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>88</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8">
+        <v>20.33333333333333</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>3.2</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>6.2</v>
+      </c>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9">
+        <v>13.81666666666667</v>
+      </c>
+      <c r="J9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C10">
+        <v>5.1</v>
+      </c>
+      <c r="D10">
+        <v>3.5</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G10">
+        <v>81</v>
+      </c>
+      <c r="H10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10">
+        <v>19.03333333333333</v>
+      </c>
+      <c r="J10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>2.7</v>
+      </c>
+      <c r="C11">
+        <v>1.5</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>2.7</v>
+      </c>
+      <c r="G11">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11">
+        <v>5.816666666666666</v>
+      </c>
+      <c r="J11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>7.7</v>
+      </c>
+      <c r="C12">
+        <v>4.9</v>
+      </c>
+      <c r="D12">
+        <v>4.5</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G12">
         <v>85</v>
       </c>
-      <c r="C2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D2" t="n">
-        <v>88</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12">
+        <v>19.8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>5.9</v>
+      </c>
+      <c r="C13">
+        <v>3.1</v>
+      </c>
+      <c r="D13">
+        <v>2.1</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>6.4</v>
+      </c>
+      <c r="G13">
+        <v>62</v>
+      </c>
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13">
+        <v>14.25</v>
+      </c>
+      <c r="J13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>4.5</v>
+      </c>
+      <c r="C14">
+        <v>2.8</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>4.3</v>
+      </c>
+      <c r="G14">
+        <v>41</v>
+      </c>
+      <c r="H14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14">
+        <v>9.6</v>
+      </c>
+      <c r="J14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15">
+        <v>3.3</v>
+      </c>
+      <c r="C15">
+        <v>2.2</v>
+      </c>
+      <c r="D15">
+        <v>1.1</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>4.4</v>
+      </c>
+      <c r="G15">
+        <v>42</v>
+      </c>
+      <c r="H15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15">
+        <v>9.5</v>
+      </c>
+      <c r="J15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>1.1</v>
+      </c>
+      <c r="C16">
+        <v>1.1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>1.9</v>
+      </c>
+      <c r="G16">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>3.85</v>
+      </c>
+      <c r="J16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17">
+        <v>8.9</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G17">
         <v>95</v>
       </c>
-      <c r="F2" t="n">
-        <v>89.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="n">
-        <v>75</v>
-      </c>
-      <c r="D3" t="n">
-        <v>80</v>
-      </c>
-      <c r="E3" t="n">
-        <v>85</v>
-      </c>
-      <c r="F3" t="n">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Carol</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>92</v>
-      </c>
-      <c r="C4" t="n">
-        <v>88</v>
-      </c>
-      <c r="D4" t="n">
-        <v>91</v>
-      </c>
-      <c r="E4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>92.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>60</v>
-      </c>
-      <c r="C5" t="n">
-        <v>65</v>
-      </c>
-      <c r="D5" t="n">
-        <v>70</v>
-      </c>
-      <c r="E5" t="n">
-        <v>80</v>
-      </c>
-      <c r="F5" t="n">
-        <v>68.75</v>
+      <c r="H17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17">
+        <v>22.46666666666667</v>
+      </c>
+      <c r="J17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18">
+        <v>2.5</v>
+      </c>
+      <c r="C18">
+        <v>1.6</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <v>3.2</v>
+      </c>
+      <c r="G18">
+        <v>30</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>6.883333333333333</v>
+      </c>
+      <c r="J18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19">
+        <v>1.9</v>
+      </c>
+      <c r="C19">
+        <v>0.9</v>
+      </c>
+      <c r="D19">
+        <v>0.5</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>2.6</v>
+      </c>
+      <c r="G19">
+        <v>24</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19">
+        <v>5.316666666666666</v>
+      </c>
+      <c r="J19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20">
+        <v>6.1</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>3.2</v>
+      </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20">
+        <v>6.9</v>
+      </c>
+      <c r="G20">
+        <v>67</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20">
+        <v>15.2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21">
+        <v>7.4</v>
+      </c>
+      <c r="C21">
+        <v>2.5</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>7</v>
+      </c>
+      <c r="F21">
+        <v>7.1</v>
+      </c>
+      <c r="G21">
+        <v>69</v>
+      </c>
+      <c r="H21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21">
+        <v>16</v>
+      </c>
+      <c r="J21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22">
+        <v>2.7</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>1.2</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>3.2</v>
+      </c>
+      <c r="G22">
+        <v>30</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22">
+        <v>7.183333333333334</v>
+      </c>
+      <c r="J22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23">
+        <v>4.8</v>
+      </c>
+      <c r="C23">
+        <v>2.9</v>
+      </c>
+      <c r="D23">
+        <v>2.1</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23">
+        <v>5.6</v>
+      </c>
+      <c r="G23">
+        <v>54</v>
+      </c>
+      <c r="H23" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23">
+        <v>12.4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24">
+        <v>3.8</v>
+      </c>
+      <c r="C24">
+        <v>2.2</v>
+      </c>
+      <c r="D24">
+        <v>0.3</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>3.7</v>
+      </c>
+      <c r="G24">
+        <v>35</v>
+      </c>
+      <c r="H24" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24">
+        <v>8</v>
+      </c>
+      <c r="J24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25">
+        <v>6.9</v>
+      </c>
+      <c r="C25">
+        <v>5.1</v>
+      </c>
+      <c r="D25">
+        <v>3.8</v>
+      </c>
+      <c r="E25">
+        <v>7</v>
+      </c>
+      <c r="F25">
+        <v>7.8</v>
+      </c>
+      <c r="G25">
+        <v>76</v>
+      </c>
+      <c r="H25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25">
+        <v>17.76666666666667</v>
+      </c>
+      <c r="J25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26">
+        <v>7.8</v>
+      </c>
+      <c r="C26">
+        <v>5.8</v>
+      </c>
+      <c r="D26">
+        <v>4.5</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G26">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26">
+        <v>20.15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:J26"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="3">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>